--- a/output/yearly_total_coral_cover_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_9_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250006764713332</v>
+        <v>1.279655545381586</v>
       </c>
       <c r="C3" t="n">
-        <v>4.636123764535847</v>
+        <v>4.584199128458232</v>
       </c>
       <c r="D3" t="n">
-        <v>6.080223789476761</v>
+        <v>6.047786845328448</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96635431872594</v>
+        <v>11.91164151916827</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.361599162706957</v>
+        <v>1.450918160313214</v>
       </c>
       <c r="C4" t="n">
-        <v>5.127529840952421</v>
+        <v>4.978422170871639</v>
       </c>
       <c r="D4" t="n">
-        <v>6.383928042977847</v>
+        <v>6.21857338408696</v>
       </c>
       <c r="E4" t="n">
-        <v>12.87305704663722</v>
+        <v>12.64791371527181</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.51258022038116</v>
+        <v>1.676536814495626</v>
       </c>
       <c r="C5" t="n">
-        <v>5.746498738890366</v>
+        <v>5.457379746119922</v>
       </c>
       <c r="D5" t="n">
-        <v>6.817846979661005</v>
+        <v>6.431619127306848</v>
       </c>
       <c r="E5" t="n">
-        <v>14.07692593893253</v>
+        <v>13.5655356879224</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.682401685229034</v>
+        <v>1.933309284271682</v>
       </c>
       <c r="C6" t="n">
-        <v>6.491409809197802</v>
+        <v>6.019052237745209</v>
       </c>
       <c r="D6" t="n">
-        <v>7.159041773900176</v>
+        <v>6.669258377179739</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33285326832701</v>
+        <v>14.62161989919663</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.877425386889343</v>
+        <v>2.228471510258928</v>
       </c>
       <c r="C7" t="n">
-        <v>7.42074441487348</v>
+        <v>6.696209577471723</v>
       </c>
       <c r="D7" t="n">
-        <v>7.602500347755981</v>
+        <v>7.01601600141491</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9006701495188</v>
+        <v>15.94069708914556</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.111196489488057</v>
+        <v>1.438638653428567</v>
       </c>
       <c r="C8" t="n">
-        <v>5.103660692128882</v>
+        <v>4.400517524295463</v>
       </c>
       <c r="D8" t="n">
-        <v>5.879646166110146</v>
+        <v>5.233681278320194</v>
       </c>
       <c r="E8" t="n">
-        <v>12.09450334772709</v>
+        <v>11.07283745604422</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.364462712817103</v>
+        <v>1.863732027954086</v>
       </c>
       <c r="C9" t="n">
-        <v>6.312692403182959</v>
+        <v>5.411879025856962</v>
       </c>
       <c r="D9" t="n">
-        <v>6.492145623057818</v>
+        <v>5.638959148434581</v>
       </c>
       <c r="E9" t="n">
-        <v>14.16930073905788</v>
+        <v>12.91457020224563</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.635962571166732</v>
+        <v>2.330883492098905</v>
       </c>
       <c r="C10" t="n">
-        <v>7.681302181311346</v>
+        <v>6.624221621915151</v>
       </c>
       <c r="D10" t="n">
-        <v>7.136604417428475</v>
+        <v>6.070321227666835</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45386916990655</v>
+        <v>15.02542634168089</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.907399725387307</v>
+        <v>2.824656393772109</v>
       </c>
       <c r="C11" t="n">
-        <v>9.217731839258905</v>
+        <v>7.965618333512751</v>
       </c>
       <c r="D11" t="n">
-        <v>7.718796355814046</v>
+        <v>6.559152425776828</v>
       </c>
       <c r="E11" t="n">
-        <v>18.84392792046026</v>
+        <v>17.34942715306169</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.181369394720281</v>
+        <v>3.330975948594515</v>
       </c>
       <c r="C12" t="n">
-        <v>10.80604493116809</v>
+        <v>9.396257417660483</v>
       </c>
       <c r="D12" t="n">
-        <v>8.314919738150355</v>
+        <v>6.991114054065787</v>
       </c>
       <c r="E12" t="n">
-        <v>21.30233406403872</v>
+        <v>19.71834742032079</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.448875714467257</v>
+        <v>3.834476418617663</v>
       </c>
       <c r="C13" t="n">
-        <v>12.45763848042576</v>
+        <v>10.8866179224068</v>
       </c>
       <c r="D13" t="n">
-        <v>8.822819748414444</v>
+        <v>7.40174344221743</v>
       </c>
       <c r="E13" t="n">
-        <v>23.72933394330746</v>
+        <v>22.12283778324189</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.422365891389821</v>
+        <v>2.203719254245773</v>
       </c>
       <c r="C14" t="n">
-        <v>8.707974509467656</v>
+        <v>7.592768022305535</v>
       </c>
       <c r="D14" t="n">
-        <v>6.688116965273227</v>
+        <v>5.678683975766655</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8184573661307</v>
+        <v>15.47517125231796</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.441480519191507</v>
+        <v>2.318181219083908</v>
       </c>
       <c r="C15" t="n">
-        <v>9.457587969045308</v>
+        <v>8.267297417462391</v>
       </c>
       <c r="D15" t="n">
-        <v>6.756996384203182</v>
+        <v>5.662455686215456</v>
       </c>
       <c r="E15" t="n">
-        <v>17.65606487244</v>
+        <v>16.24793432276175</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.654136889408408</v>
+        <v>2.738693213243945</v>
       </c>
       <c r="C16" t="n">
-        <v>11.18312736898359</v>
+        <v>9.900523080770343</v>
       </c>
       <c r="D16" t="n">
-        <v>7.294552339663523</v>
+        <v>6.105459520279786</v>
       </c>
       <c r="E16" t="n">
-        <v>20.13181659805552</v>
+        <v>18.74467581429407</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.315139407131985</v>
+        <v>2.221950309113637</v>
       </c>
       <c r="C17" t="n">
-        <v>10.32266477611943</v>
+        <v>9.338727774492147</v>
       </c>
       <c r="D17" t="n">
-        <v>6.808223979410781</v>
+        <v>5.649830410738843</v>
       </c>
       <c r="E17" t="n">
-        <v>18.44602816266219</v>
+        <v>17.21050849434463</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.484942490058513</v>
+        <v>2.571413221917331</v>
       </c>
       <c r="C18" t="n">
-        <v>12.02557489147482</v>
+        <v>11.03583576091544</v>
       </c>
       <c r="D18" t="n">
-        <v>7.347066024363684</v>
+        <v>6.049097384578977</v>
       </c>
       <c r="E18" t="n">
-        <v>20.85758340589702</v>
+        <v>19.65634636741175</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.47657799961833</v>
+        <v>2.610064629033528</v>
       </c>
       <c r="C19" t="n">
-        <v>12.8426736882424</v>
+        <v>11.96469671633447</v>
       </c>
       <c r="D19" t="n">
-        <v>7.478217700174017</v>
+        <v>6.1253202763367</v>
       </c>
       <c r="E19" t="n">
-        <v>21.79746938803475</v>
+        <v>20.7000816217047</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.633117671060484</v>
+        <v>2.937556028216179</v>
       </c>
       <c r="C20" t="n">
-        <v>14.69620353638333</v>
+        <v>13.92305758433488</v>
       </c>
       <c r="D20" t="n">
-        <v>7.9635152253373</v>
+        <v>6.50153581408112</v>
       </c>
       <c r="E20" t="n">
-        <v>24.29283643278112</v>
+        <v>23.36214942663218</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.967581084874529</v>
+        <v>1.760646697842145</v>
       </c>
       <c r="C21" t="n">
-        <v>10.74173360115422</v>
+        <v>10.35382544825222</v>
       </c>
       <c r="D21" t="n">
-        <v>6.672006485446537</v>
+        <v>5.408281205585956</v>
       </c>
       <c r="E21" t="n">
-        <v>18.38132117147529</v>
+        <v>17.52275335168032</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_9_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.279655545381586</v>
+        <v>1.251263401774768</v>
       </c>
       <c r="C3" t="n">
-        <v>4.584199128458232</v>
+        <v>4.614662759721011</v>
       </c>
       <c r="D3" t="n">
-        <v>6.047786845328448</v>
+        <v>6.112837448211841</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91164151916827</v>
+        <v>11.97876360970762</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.450918160313214</v>
+        <v>1.372975487653309</v>
       </c>
       <c r="C4" t="n">
-        <v>4.978422170871639</v>
+        <v>5.111663459400467</v>
       </c>
       <c r="D4" t="n">
-        <v>6.21857338408696</v>
+        <v>6.516306652718972</v>
       </c>
       <c r="E4" t="n">
-        <v>12.64791371527181</v>
+        <v>13.00094559977275</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.676536814495626</v>
+        <v>1.53774515469851</v>
       </c>
       <c r="C5" t="n">
-        <v>5.457379746119922</v>
+        <v>5.718369905740171</v>
       </c>
       <c r="D5" t="n">
-        <v>6.431619127306848</v>
+        <v>6.846037150195685</v>
       </c>
       <c r="E5" t="n">
-        <v>13.5655356879224</v>
+        <v>14.10215221063437</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.933309284271682</v>
+        <v>1.728362840910015</v>
       </c>
       <c r="C6" t="n">
-        <v>6.019052237745209</v>
+        <v>6.481975662773696</v>
       </c>
       <c r="D6" t="n">
-        <v>6.669258377179739</v>
+        <v>7.329022957824765</v>
       </c>
       <c r="E6" t="n">
-        <v>14.62161989919663</v>
+        <v>15.53936146150848</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.228471510258928</v>
+        <v>1.957222576407301</v>
       </c>
       <c r="C7" t="n">
-        <v>6.696209577471723</v>
+        <v>7.34528040113804</v>
       </c>
       <c r="D7" t="n">
-        <v>7.01601600141491</v>
+        <v>7.781015050683784</v>
       </c>
       <c r="E7" t="n">
-        <v>15.94069708914556</v>
+        <v>17.08351802822913</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.438638653428567</v>
+        <v>1.207138077435331</v>
       </c>
       <c r="C8" t="n">
-        <v>4.400517524295463</v>
+        <v>4.965735868411246</v>
       </c>
       <c r="D8" t="n">
-        <v>5.233681278320194</v>
+        <v>6.154095761077884</v>
       </c>
       <c r="E8" t="n">
-        <v>11.07283745604422</v>
+        <v>12.32696970692446</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.863732027954086</v>
+        <v>1.523233727548168</v>
       </c>
       <c r="C9" t="n">
-        <v>5.411879025856962</v>
+        <v>6.022392637162753</v>
       </c>
       <c r="D9" t="n">
-        <v>5.638959148434581</v>
+        <v>6.750128912410736</v>
       </c>
       <c r="E9" t="n">
-        <v>12.91457020224563</v>
+        <v>14.29575527712166</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.330883492098905</v>
+        <v>1.84993487644676</v>
       </c>
       <c r="C10" t="n">
-        <v>6.624221621915151</v>
+        <v>7.272663939714317</v>
       </c>
       <c r="D10" t="n">
-        <v>6.070321227666835</v>
+        <v>7.365793762981901</v>
       </c>
       <c r="E10" t="n">
-        <v>15.02542634168089</v>
+        <v>16.48839257914298</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.824656393772109</v>
+        <v>2.178908050873059</v>
       </c>
       <c r="C11" t="n">
-        <v>7.965618333512751</v>
+        <v>8.631827584090576</v>
       </c>
       <c r="D11" t="n">
-        <v>6.559152425776828</v>
+        <v>7.979633083754635</v>
       </c>
       <c r="E11" t="n">
-        <v>17.34942715306169</v>
+        <v>18.79036871871827</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.330975948594515</v>
+        <v>2.50617966991834</v>
       </c>
       <c r="C12" t="n">
-        <v>9.396257417660483</v>
+        <v>10.06212315907013</v>
       </c>
       <c r="D12" t="n">
-        <v>6.991114054065787</v>
+        <v>8.596454455451214</v>
       </c>
       <c r="E12" t="n">
-        <v>19.71834742032079</v>
+        <v>21.16475728443968</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.834476418617663</v>
+        <v>2.821506234548612</v>
       </c>
       <c r="C13" t="n">
-        <v>10.8866179224068</v>
+        <v>11.54227018419786</v>
       </c>
       <c r="D13" t="n">
-        <v>7.40174344221743</v>
+        <v>9.09406722781185</v>
       </c>
       <c r="E13" t="n">
-        <v>22.12283778324189</v>
+        <v>23.45784364655832</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.203719254245773</v>
+        <v>1.622279176405599</v>
       </c>
       <c r="C14" t="n">
-        <v>7.592768022305535</v>
+        <v>8.122833242782471</v>
       </c>
       <c r="D14" t="n">
-        <v>5.678683975766655</v>
+        <v>6.855701298388157</v>
       </c>
       <c r="E14" t="n">
-        <v>15.47517125231796</v>
+        <v>16.60081371757623</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.318181219083908</v>
+        <v>1.655982575092392</v>
       </c>
       <c r="C15" t="n">
-        <v>8.267297417462391</v>
+        <v>8.745114025119312</v>
       </c>
       <c r="D15" t="n">
-        <v>5.662455686215456</v>
+        <v>6.919279279715179</v>
       </c>
       <c r="E15" t="n">
-        <v>16.24793432276175</v>
+        <v>17.32037587992689</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.738693213243945</v>
+        <v>1.925374145137717</v>
       </c>
       <c r="C16" t="n">
-        <v>9.900523080770343</v>
+        <v>10.32512896285709</v>
       </c>
       <c r="D16" t="n">
-        <v>6.105459520279786</v>
+        <v>7.517065456831064</v>
       </c>
       <c r="E16" t="n">
-        <v>18.74467581429407</v>
+        <v>19.76756856482587</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.221950309113637</v>
+        <v>1.549227329732594</v>
       </c>
       <c r="C17" t="n">
-        <v>9.338727774492147</v>
+        <v>9.527684755128531</v>
       </c>
       <c r="D17" t="n">
-        <v>5.649830410738843</v>
+        <v>7.026437041633719</v>
       </c>
       <c r="E17" t="n">
-        <v>17.21050849434463</v>
+        <v>18.10334912649484</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.571413221917331</v>
+        <v>1.763110884579804</v>
       </c>
       <c r="C18" t="n">
-        <v>11.03583576091544</v>
+        <v>11.13677905986609</v>
       </c>
       <c r="D18" t="n">
-        <v>6.049097384578977</v>
+        <v>7.585012215441983</v>
       </c>
       <c r="E18" t="n">
-        <v>19.65634636741175</v>
+        <v>20.48490215988788</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.610064629033528</v>
+        <v>1.762561105865426</v>
       </c>
       <c r="C19" t="n">
-        <v>11.96469671633447</v>
+        <v>11.94511084963475</v>
       </c>
       <c r="D19" t="n">
-        <v>6.1253202763367</v>
+        <v>7.746980951688624</v>
       </c>
       <c r="E19" t="n">
-        <v>20.7000816217047</v>
+        <v>21.4546529071888</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.937556028216179</v>
+        <v>1.955081830668226</v>
       </c>
       <c r="C20" t="n">
-        <v>13.92305758433488</v>
+        <v>13.8014190437787</v>
       </c>
       <c r="D20" t="n">
-        <v>6.50153581408112</v>
+        <v>8.239189980689805</v>
       </c>
       <c r="E20" t="n">
-        <v>23.36214942663218</v>
+        <v>23.99569085513674</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.760646697842145</v>
+        <v>1.157274376289098</v>
       </c>
       <c r="C21" t="n">
-        <v>10.35382544825222</v>
+        <v>10.22066118964818</v>
       </c>
       <c r="D21" t="n">
-        <v>5.408281205585956</v>
+        <v>6.90237358424805</v>
       </c>
       <c r="E21" t="n">
-        <v>17.52275335168032</v>
+        <v>18.28030915018533</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_9_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251263401774768</v>
+        <v>2.594797974116019</v>
       </c>
       <c r="C3" t="n">
-        <v>4.614662759721011</v>
+        <v>7.798480605609916</v>
       </c>
       <c r="D3" t="n">
-        <v>6.112837448211841</v>
+        <v>8.211698850028316</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97876360970762</v>
+        <v>18.60497742975425</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.372975487653309</v>
+        <v>1.070554885948407</v>
       </c>
       <c r="C4" t="n">
-        <v>5.111663459400467</v>
+        <v>4.70553608301636</v>
       </c>
       <c r="D4" t="n">
-        <v>6.516306652718972</v>
+        <v>5.790730072378904</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00094559977275</v>
+        <v>11.56682104134367</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.53774515469851</v>
+        <v>1.155717891354397</v>
       </c>
       <c r="C5" t="n">
-        <v>5.718369905740171</v>
+        <v>5.584470911145525</v>
       </c>
       <c r="D5" t="n">
-        <v>6.846037150195685</v>
+        <v>6.077917983381005</v>
       </c>
       <c r="E5" t="n">
-        <v>14.10215221063437</v>
+        <v>12.81810678588093</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.728362840910015</v>
+        <v>1.253174796560854</v>
       </c>
       <c r="C6" t="n">
-        <v>6.481975662773696</v>
+        <v>6.676158012407205</v>
       </c>
       <c r="D6" t="n">
-        <v>7.329022957824765</v>
+        <v>6.377248741723134</v>
       </c>
       <c r="E6" t="n">
-        <v>15.53936146150848</v>
+        <v>14.30658155069119</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.957222576407301</v>
+        <v>1.356233255901383</v>
       </c>
       <c r="C7" t="n">
-        <v>7.34528040113804</v>
+        <v>7.905625398545654</v>
       </c>
       <c r="D7" t="n">
-        <v>7.781015050683784</v>
+        <v>6.690097584560559</v>
       </c>
       <c r="E7" t="n">
-        <v>17.08351802822913</v>
+        <v>15.9519562390076</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.207138077435331</v>
+        <v>1.469666171788284</v>
       </c>
       <c r="C8" t="n">
-        <v>4.965735868411246</v>
+        <v>9.266550015496609</v>
       </c>
       <c r="D8" t="n">
-        <v>6.154095761077884</v>
+        <v>7.015301487300262</v>
       </c>
       <c r="E8" t="n">
-        <v>12.32696970692446</v>
+        <v>17.75151767458516</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.523233727548168</v>
+        <v>1.563534772863993</v>
       </c>
       <c r="C9" t="n">
-        <v>6.022392637162753</v>
+        <v>10.76452498171529</v>
       </c>
       <c r="D9" t="n">
-        <v>6.750128912410736</v>
+        <v>7.337957401140135</v>
       </c>
       <c r="E9" t="n">
-        <v>14.29575527712166</v>
+        <v>19.66601715571942</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.84993487644676</v>
+        <v>0.9877363652427159</v>
       </c>
       <c r="C10" t="n">
-        <v>7.272663939714317</v>
+        <v>7.720336318995364</v>
       </c>
       <c r="D10" t="n">
-        <v>7.365793762981901</v>
+        <v>5.745747161443756</v>
       </c>
       <c r="E10" t="n">
-        <v>16.48839257914298</v>
+        <v>14.45381984568183</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.178908050873059</v>
+        <v>0.9090001993621217</v>
       </c>
       <c r="C11" t="n">
-        <v>8.631827584090576</v>
+        <v>8.335519065430502</v>
       </c>
       <c r="D11" t="n">
-        <v>7.979633083754635</v>
+        <v>5.538058434610343</v>
       </c>
       <c r="E11" t="n">
-        <v>18.79036871871827</v>
+        <v>14.78257769940297</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.50617966991834</v>
+        <v>0.9705754153724816</v>
       </c>
       <c r="C12" t="n">
-        <v>10.06212315907013</v>
+        <v>9.99625329941145</v>
       </c>
       <c r="D12" t="n">
-        <v>8.596454455451214</v>
+        <v>5.850754895889994</v>
       </c>
       <c r="E12" t="n">
-        <v>21.16475728443968</v>
+        <v>16.81758361067392</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.821506234548612</v>
+        <v>0.7624350845951154</v>
       </c>
       <c r="C13" t="n">
-        <v>11.54227018419786</v>
+        <v>9.617357590434436</v>
       </c>
       <c r="D13" t="n">
-        <v>9.09406722781185</v>
+        <v>5.268136720804725</v>
       </c>
       <c r="E13" t="n">
-        <v>23.45784364655832</v>
+        <v>15.64792939583428</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.622279176405599</v>
+        <v>0.8204367389620171</v>
       </c>
       <c r="C14" t="n">
-        <v>8.122833242782471</v>
+        <v>11.47597289168337</v>
       </c>
       <c r="D14" t="n">
-        <v>6.855701298388157</v>
+        <v>5.528456942062809</v>
       </c>
       <c r="E14" t="n">
-        <v>16.60081371757623</v>
+        <v>17.8248665727082</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.655982575092392</v>
+        <v>0.7941651703963722</v>
       </c>
       <c r="C15" t="n">
-        <v>8.745114025119312</v>
+        <v>12.59130700604704</v>
       </c>
       <c r="D15" t="n">
-        <v>6.919279279715179</v>
+        <v>5.499731004236548</v>
       </c>
       <c r="E15" t="n">
-        <v>17.32037587992689</v>
+        <v>18.88520318067996</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.925374145137717</v>
+        <v>0.8670697549137405</v>
       </c>
       <c r="C16" t="n">
-        <v>10.32512896285709</v>
+        <v>14.8649070618811</v>
       </c>
       <c r="D16" t="n">
-        <v>7.517065456831064</v>
+        <v>5.798300116052087</v>
       </c>
       <c r="E16" t="n">
-        <v>19.76756856482587</v>
+        <v>21.53027693284693</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.549227329732594</v>
+        <v>0.5230653593456582</v>
       </c>
       <c r="C17" t="n">
-        <v>9.527684755128531</v>
+        <v>11.27529384345828</v>
       </c>
       <c r="D17" t="n">
-        <v>7.026437041633719</v>
+        <v>4.752513009057258</v>
       </c>
       <c r="E17" t="n">
-        <v>18.10334912649484</v>
+        <v>16.55087221186119</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.763110884579804</v>
+        <v>0.4145626030723007</v>
       </c>
       <c r="C18" t="n">
-        <v>11.13677905986609</v>
+        <v>10.42272450213626</v>
       </c>
       <c r="D18" t="n">
-        <v>7.585012215441983</v>
+        <v>4.218177186066845</v>
       </c>
       <c r="E18" t="n">
-        <v>20.48490215988788</v>
+        <v>15.05546429127541</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.762561105865426</v>
+        <v>0.4847870163570751</v>
       </c>
       <c r="C19" t="n">
-        <v>11.94511084963475</v>
+        <v>13.01142630112538</v>
       </c>
       <c r="D19" t="n">
-        <v>7.746980951688624</v>
+        <v>4.572597924776987</v>
       </c>
       <c r="E19" t="n">
-        <v>21.4546529071888</v>
+        <v>18.06881124225944</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.955081830668226</v>
+        <v>0.5475697820436586</v>
       </c>
       <c r="C20" t="n">
-        <v>13.8014190437787</v>
+        <v>15.71972460544584</v>
       </c>
       <c r="D20" t="n">
-        <v>8.239189980689805</v>
+        <v>4.902121541707428</v>
       </c>
       <c r="E20" t="n">
-        <v>23.99569085513674</v>
+        <v>21.16941592919693</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.157274376289098</v>
+        <v>0.6007903250908782</v>
       </c>
       <c r="C21" t="n">
-        <v>10.22066118964818</v>
+        <v>18.36129351830865</v>
       </c>
       <c r="D21" t="n">
-        <v>6.90237358424805</v>
+        <v>5.193101743769142</v>
       </c>
       <c r="E21" t="n">
-        <v>18.28030915018533</v>
+        <v>24.15518558716867</v>
       </c>
     </row>
   </sheetData>
